--- a/data/LCIs/ni_lci_sofia_roy.xlsx
+++ b/data/LCIs/ni_lci_sofia_roy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/LCIs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{85F0669E-F0AF-42BA-BF43-9EA77600C7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98032053-1D03-44A5-B3DF-3557D1489F29}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{85F0669E-F0AF-42BA-BF43-9EA77600C7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2B2D52-CECE-453A-A3F2-8F28373C0F3D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pyrometallurgical sulfide ore" sheetId="6" r:id="rId1"/>
@@ -321,9 +321,6 @@
     <t>ecoinvent-3.10-cutoff</t>
   </si>
   <si>
-    <t>Nickel</t>
-  </si>
-  <si>
     <t>Database</t>
   </si>
   <si>
@@ -346,6 +343,9 @@
   </si>
   <si>
     <t>POX leaching of 19% Ni concentrate and refining to nickel metal (mining CA)</t>
+  </si>
+  <si>
+    <t>Nickel - Sofia Roy</t>
   </si>
 </sst>
 </file>
@@ -570,10 +570,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -862,21 +858,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="55" customWidth="1"/>
     <col min="3" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -884,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1323,10 +1319,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -1399,12 +1395,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721FFB66-19E7-4922-B5E1-4E4E9E0C2D29}">
   <dimension ref="A1:N44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="97.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1412,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2020,7 +2016,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D31">
         <f>0.0015</f>
@@ -2104,7 +2100,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D35">
         <f>0.00027</f>
@@ -2293,7 +2289,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>0.08</v>
